--- a/e2e/downloadedFile/Non_Regular_Cutah_Semester_1.xlsx
+++ b/e2e/downloadedFile/Non_Regular_Cutah_Semester_1.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="53">
   <si>
     <t>DAFTAR PEMBAYARAN</t>
   </si>
@@ -71,6 +71,72 @@
     <t>JUN</t>
   </si>
   <si>
+    <t>CELIA MARIA REGO DE FATIMA</t>
+  </si>
+  <si>
+    <t>IV</t>
+  </si>
+  <si>
+    <t>Local</t>
+  </si>
+  <si>
+    <t>0,00</t>
+  </si>
+  <si>
+    <t>0,50</t>
+  </si>
+  <si>
+    <t>125,00</t>
+  </si>
+  <si>
+    <t>ADROALDINO DA SILVA NORONHA TOME</t>
+  </si>
+  <si>
+    <t>VI</t>
+  </si>
+  <si>
+    <t>0,25</t>
+  </si>
+  <si>
+    <t>62,50</t>
+  </si>
+  <si>
+    <t>DIAN EVIYANTI APLUGI</t>
+  </si>
+  <si>
+    <t>III</t>
+  </si>
+  <si>
+    <t>FRIESCA AMELIA</t>
+  </si>
+  <si>
+    <t>HERU YULIANTO</t>
+  </si>
+  <si>
+    <t>II</t>
+  </si>
+  <si>
+    <t>SYALDY KHARISMA ANANDA</t>
+  </si>
+  <si>
+    <t>AGOSTINHO GOMES FERNANDES</t>
+  </si>
+  <si>
+    <t>Expat</t>
+  </si>
+  <si>
+    <t>AHMAD RIYANA SAPUTRA</t>
+  </si>
+  <si>
+    <t>1,00</t>
+  </si>
+  <si>
+    <t>250,00</t>
+  </si>
+  <si>
+    <t>CLAUDIO DA COSTA ALVES</t>
+  </si>
+  <si>
     <t>Lestari Putri Cantika</t>
   </si>
   <si>
@@ -80,58 +146,13 @@
     <t>Homestaff</t>
   </si>
   <si>
-    <t>0,00</t>
-  </si>
-  <si>
-    <t>1,50</t>
-  </si>
-  <si>
-    <t>105,00</t>
-  </si>
-  <si>
-    <t>HELENA</t>
-  </si>
-  <si>
-    <t>II</t>
-  </si>
-  <si>
-    <t>108,75</t>
-  </si>
-  <si>
-    <t>CELIA MARIA REGO DE FATIMA</t>
-  </si>
-  <si>
-    <t>IV</t>
-  </si>
-  <si>
-    <t>Local</t>
-  </si>
-  <si>
-    <t>4,00</t>
-  </si>
-  <si>
-    <t>240,00</t>
-  </si>
-  <si>
-    <t>0000002</t>
-  </si>
-  <si>
-    <t>Syifa Hadju</t>
-  </si>
-  <si>
-    <t>3,00</t>
-  </si>
-  <si>
-    <t>67,50</t>
-  </si>
-  <si>
     <t>GRAND TOTAL</t>
   </si>
   <si>
-    <t>521,25</t>
-  </si>
-  <si>
-    <t>DILI, 14 August 2026</t>
+    <t>1.312,50</t>
+  </si>
+  <si>
+    <t>DILI, 18 August 2026</t>
   </si>
   <si>
     <t>PREPARED BY</t>
@@ -245,7 +266,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="514350" cy="333375"/>
@@ -564,11 +585,11 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:N24"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="true" style="0"/>
-    <col min="2" max="2" width="31.707" bestFit="true" customWidth="true" style="0"/>
+    <col min="2" max="2" width="38.848" bestFit="true" customWidth="true" style="0"/>
     <col min="3" max="3" width="6.998" bestFit="true" customWidth="true" style="0"/>
     <col min="4" max="4" width="11.711" bestFit="true" customWidth="true" style="0"/>
     <col min="5" max="5" width="5.856" bestFit="true" customWidth="true" style="0"/>
@@ -579,7 +600,7 @@
     <col min="10" max="10" width="5.856" bestFit="true" customWidth="true" style="0"/>
     <col min="11" max="11" width="5.856" bestFit="true" customWidth="true" style="0"/>
     <col min="12" max="12" width="5.856" bestFit="true" customWidth="true" style="0"/>
-    <col min="13" max="13" width="8.141" bestFit="true" customWidth="true" style="0"/>
+    <col min="13" max="13" width="10.569" bestFit="true" customWidth="true" style="0"/>
     <col min="14" max="14" width="5.856" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
@@ -665,7 +686,7 @@
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="3">
-        <v>999999</v>
+        <v>92003</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>18</v>
@@ -709,7 +730,7 @@
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="3">
-        <v>84016</v>
+        <v>24016</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>24</v>
@@ -727,25 +748,25 @@
         <v>21</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N8" s="3" t="s">
         <v>21</v>
@@ -753,173 +774,437 @@
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="3">
-        <v>92003</v>
+        <v>79001</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="3">
+        <v>91009</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M9" s="3" t="s">
+      <c r="D10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="3">
+        <v>74003</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="3" t="s">
+      <c r="C11" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="D11" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="3">
+        <v>91015</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C12" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="3">
+        <v>26013</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="3">
+        <v>95008</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="4" t="s">
+      <c r="D14" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="N11" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12"/>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" t="s">
+      <c r="H14" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M14" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="H13"/>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="A14" s="5" t="s">
+      <c r="N14" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="3">
+        <v>24005</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5" t="s">
+      <c r="C15" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" s="3">
+        <v>999999</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5"/>
-      <c r="M14" s="5"/>
-      <c r="N14" s="5"/>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="A15" t="s">
+      <c r="C16" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="F15"/>
-      <c r="J15" t="s">
+      <c r="D16" s="3" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" customHeight="1" ht="37.5">
-      <c r="A16"/>
-      <c r="F16"/>
-      <c r="J16"/>
+      <c r="E16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="17" spans="1:14">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="F17"/>
-      <c r="J17" s="1" t="s">
-        <v>18</v>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="N17" s="4" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:14">
-      <c r="A18" t="s">
-        <v>44</v>
-      </c>
-      <c r="F18"/>
-      <c r="J18" t="s">
+      <c r="A18"/>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" t="s">
         <v>45</v>
+      </c>
+      <c r="H19"/>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="5"/>
+      <c r="M20" s="5"/>
+      <c r="N20" s="5"/>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" t="s">
+        <v>48</v>
+      </c>
+      <c r="F21"/>
+      <c r="J21" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" customHeight="1" ht="37.5">
+      <c r="A22"/>
+      <c r="F22"/>
+      <c r="J22"/>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F23"/>
+      <c r="J23" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" t="s">
+        <v>51</v>
+      </c>
+      <c r="F24"/>
+      <c r="J24" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -937,24 +1222,24 @@
     <mergeCell ref="G5:L5"/>
     <mergeCell ref="M5:M6"/>
     <mergeCell ref="N5:N6"/>
-    <mergeCell ref="A11:L11"/>
-    <mergeCell ref="A12:M12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="H13:N13"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="H14:N14"/>
-    <mergeCell ref="A15:E15"/>
-    <mergeCell ref="F15:I15"/>
-    <mergeCell ref="J15:N15"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="F16:I16"/>
-    <mergeCell ref="J16:N16"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="F17:I17"/>
-    <mergeCell ref="J17:N17"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="F18:I18"/>
-    <mergeCell ref="J18:N18"/>
+    <mergeCell ref="A17:L17"/>
+    <mergeCell ref="A18:M18"/>
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="H19:N19"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="H20:N20"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="F21:I21"/>
+    <mergeCell ref="J21:N21"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="J22:N22"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="F23:I23"/>
+    <mergeCell ref="J23:N23"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="F24:I24"/>
+    <mergeCell ref="J24:N24"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
